--- a/conciliador_clientes/plantilla/PLANTILLA DE SOTSEGUROS.xlsx
+++ b/conciliador_clientes/plantilla/PLANTILLA DE SOTSEGUROS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ejecutiva8\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danie\Documents\EMPRESA\SEGUROS UNIÓN\AUTOMATIZACIONES\migraciones\migracion-softseguros\conciliador_clientes\plantilla\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{25D53D6F-CDB8-49F8-AFB8-39227AB22575}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEFECB20-C5CD-41E5-A34A-A04FBBE4E3F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Clientes" sheetId="1" r:id="rId1"/>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1242" uniqueCount="1126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2049" uniqueCount="1519">
   <si>
     <t>NOMBRES</t>
   </si>
@@ -3435,13 +3435,1192 @@
   </si>
   <si>
     <t>Pedro Antonio Alzate Galindo</t>
+  </si>
+  <si>
+    <t>ADRIANA</t>
+  </si>
+  <si>
+    <t>ADRIANA GISELA</t>
+  </si>
+  <si>
+    <t>ALEJANDRO</t>
+  </si>
+  <si>
+    <t>ALFONSO</t>
+  </si>
+  <si>
+    <t>ALVIS ALBERTO</t>
+  </si>
+  <si>
+    <t>ANA MARIA</t>
+  </si>
+  <si>
+    <t>ANDREA</t>
+  </si>
+  <si>
+    <t>ANDRES FELIPE</t>
+  </si>
+  <si>
+    <t>ANDRES</t>
+  </si>
+  <si>
+    <t>ANGEL ANDRES</t>
+  </si>
+  <si>
+    <t>ANGELICA</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>BEATRIZ ELENA</t>
+  </si>
+  <si>
+    <t>BEATRIZ</t>
+  </si>
+  <si>
+    <t>BLANCA LILIANA</t>
+  </si>
+  <si>
+    <t>CARMEN</t>
+  </si>
+  <si>
+    <t>CLAUDIA MARCELA</t>
+  </si>
+  <si>
+    <t>CLAUDIA PATRICIA</t>
+  </si>
+  <si>
+    <t>DANIEL</t>
+  </si>
+  <si>
+    <t>DARIA</t>
+  </si>
+  <si>
+    <t>DAVID SANTIAGO</t>
+  </si>
+  <si>
+    <t>DIANA MARCELA</t>
+  </si>
+  <si>
+    <t>DIANA MARIA</t>
+  </si>
+  <si>
+    <t>DIANA PINEDA</t>
+  </si>
+  <si>
+    <t>DIEGO ALBERTO</t>
+  </si>
+  <si>
+    <t>DORA</t>
+  </si>
+  <si>
+    <t>EDWIN</t>
+  </si>
+  <si>
+    <t>ELIANA</t>
+  </si>
+  <si>
+    <t>FANNY</t>
+  </si>
+  <si>
+    <t>FRANCISCO</t>
+  </si>
+  <si>
+    <t>GABRIEL</t>
+  </si>
+  <si>
+    <t>GILMA</t>
+  </si>
+  <si>
+    <t>GIOVANNI DE JESUS</t>
+  </si>
+  <si>
+    <t>GLORIA MARIA</t>
+  </si>
+  <si>
+    <t>GLORIA TERESA</t>
+  </si>
+  <si>
+    <t>GUSTAVO DE JESUS</t>
+  </si>
+  <si>
+    <t>HECTOR</t>
+  </si>
+  <si>
+    <t>HENRY ALBERTO</t>
+  </si>
+  <si>
+    <t>INGRID</t>
+  </si>
+  <si>
+    <t>ISABEL</t>
+  </si>
+  <si>
+    <t>IVAN AURELIO</t>
+  </si>
+  <si>
+    <t>IVANNA</t>
+  </si>
+  <si>
+    <t>JAIME</t>
+  </si>
+  <si>
+    <t>JAVIER DE</t>
+  </si>
+  <si>
+    <t>JENNIFER</t>
+  </si>
+  <si>
+    <t>JENNY ALEJANDRA</t>
+  </si>
+  <si>
+    <t>JENNY MARITZA</t>
+  </si>
+  <si>
+    <t>JHON</t>
+  </si>
+  <si>
+    <t>JORGE H</t>
+  </si>
+  <si>
+    <t>JORGE</t>
+  </si>
+  <si>
+    <t>JOSE HERNAN</t>
+  </si>
+  <si>
+    <t>JUAN ANTONIO</t>
+  </si>
+  <si>
+    <t>JUAN</t>
+  </si>
+  <si>
+    <t>JUAN CARLOS</t>
+  </si>
+  <si>
+    <t>JUAN GUILLERMO</t>
+  </si>
+  <si>
+    <t>JULIETH KATKERINE</t>
+  </si>
+  <si>
+    <t>JULIO CESAR</t>
+  </si>
+  <si>
+    <t>LILIANA</t>
+  </si>
+  <si>
+    <t>LINA</t>
+  </si>
+  <si>
+    <t>LORENA ROCIO</t>
+  </si>
+  <si>
+    <t>LUIS FERNANDO</t>
+  </si>
+  <si>
+    <t>LUISA MARÍA</t>
+  </si>
+  <si>
+    <t>LUZ DARY</t>
+  </si>
+  <si>
+    <t>LUZ</t>
+  </si>
+  <si>
+    <t>LUZ STELLA</t>
+  </si>
+  <si>
+    <t>BRAN</t>
+  </si>
+  <si>
+    <t>ABDEL PINZON</t>
+  </si>
+  <si>
+    <t>MARIN CERON</t>
+  </si>
+  <si>
+    <t>VELASQUEZ ARDILA</t>
+  </si>
+  <si>
+    <t>BONILLA CORDOBA</t>
+  </si>
+  <si>
+    <t>VASQUEZ BARRIOS</t>
+  </si>
+  <si>
+    <t>JARAMILLO VELEZ</t>
+  </si>
+  <si>
+    <t>TORRES PACHECO</t>
+  </si>
+  <si>
+    <t>LOMBANA GOMEZ</t>
+  </si>
+  <si>
+    <t>ORTIZ BUSTAMANTE</t>
+  </si>
+  <si>
+    <t>VARGAS PEÑUELA</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>HERRERA DUQUE</t>
+  </si>
+  <si>
+    <t>HINCAPIE LOPEZ</t>
+  </si>
+  <si>
+    <t>LOPEZ SANABRIA</t>
+  </si>
+  <si>
+    <t>MILEIDY OSORIO</t>
+  </si>
+  <si>
+    <t>GUARIN</t>
+  </si>
+  <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
+    <t>TABARES</t>
+  </si>
+  <si>
+    <t>MEJIA RIVADENEIRA</t>
+  </si>
+  <si>
+    <t>SOSA MORALES</t>
+  </si>
+  <si>
+    <t>VELANDIA SALAS</t>
+  </si>
+  <si>
+    <t>ZAPATA</t>
+  </si>
+  <si>
+    <t>JESE ARREDONDO</t>
+  </si>
+  <si>
+    <t>CASTAÑO GOMEZ</t>
+  </si>
+  <si>
+    <t>TORO QUINTERO</t>
+  </si>
+  <si>
+    <t>LONDOÑO GARCIA</t>
+  </si>
+  <si>
+    <t>MARCELA MARIN</t>
+  </si>
+  <si>
+    <t>LOPEZ JARAMILLO</t>
+  </si>
+  <si>
+    <t>SUCERQUIA</t>
+  </si>
+  <si>
+    <t>BUSTAMANTE MARIN</t>
+  </si>
+  <si>
+    <t>TOBON</t>
+  </si>
+  <si>
+    <t>LOPERA</t>
+  </si>
+  <si>
+    <t>JAVIER BETANCUR</t>
+  </si>
+  <si>
+    <t>GIL</t>
+  </si>
+  <si>
+    <t>MEJIA LOPEZ</t>
+  </si>
+  <si>
+    <t>OCAMPO GALEANO</t>
+  </si>
+  <si>
+    <t>RAMIREZ TANGARIFE</t>
+  </si>
+  <si>
+    <t>RUIZ SANTANA</t>
+  </si>
+  <si>
+    <t>CARVAJAL RAMIREZ</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>GARCIA GARCIA</t>
+  </si>
+  <si>
+    <t>RODRÍGUEZ RIVERA</t>
+  </si>
+  <si>
+    <t>AGUIRRE ALVAREZ</t>
+  </si>
+  <si>
+    <t>CERI</t>
+  </si>
+  <si>
+    <t>CASTAÑO SALAZAR</t>
+  </si>
+  <si>
+    <t>CALDERON ZAPATA</t>
+  </si>
+  <si>
+    <t>BRITO</t>
+  </si>
+  <si>
+    <t>JESUS VASQUEZ</t>
+  </si>
+  <si>
+    <t>NOREÑA PEREZ</t>
+  </si>
+  <si>
+    <t>ESCOBAR ARBELAEZ</t>
+  </si>
+  <si>
+    <t>REYES ICO</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>POSADA ALVAREZ</t>
+  </si>
+  <si>
+    <t>RINCON</t>
+  </si>
+  <si>
+    <t>GOMEZ GOMEZ</t>
+  </si>
+  <si>
+    <t>VELEZ SALDARRIAGA</t>
+  </si>
+  <si>
+    <t>CAMILO DUQUE</t>
+  </si>
+  <si>
+    <t>CAMILO ZULUAGA</t>
+  </si>
+  <si>
+    <t>AGUDELO ARISTIZÁBAL</t>
+  </si>
+  <si>
+    <t>RIVERA PIEDRAHITA</t>
+  </si>
+  <si>
+    <t>OLARTE</t>
+  </si>
+  <si>
+    <t>SEBASTIAN DIAZ</t>
+  </si>
+  <si>
+    <t>SEBASTIAN PINEDA</t>
+  </si>
+  <si>
+    <t>COSSIO CALLEJAS</t>
+  </si>
+  <si>
+    <t>VILLA ROMANO</t>
+  </si>
+  <si>
+    <t>TABORDA</t>
+  </si>
+  <si>
+    <t>LOPEZ P</t>
+  </si>
+  <si>
+    <t>MARIA MEJIA</t>
+  </si>
+  <si>
+    <t>LOPEZ ARCINIEGAS</t>
+  </si>
+  <si>
+    <t>DUQUE GOMEZ</t>
+  </si>
+  <si>
+    <t>PATIÑO RUIZ</t>
+  </si>
+  <si>
+    <t>MARTÍNEZ RESTREPO</t>
+  </si>
+  <si>
+    <t>FLOREZ TORRES</t>
+  </si>
+  <si>
+    <t>MARINA FIGUEROA</t>
+  </si>
+  <si>
+    <t>MARTINEZ OROZCO</t>
+  </si>
+  <si>
+    <t>MAIRA</t>
+  </si>
+  <si>
+    <t>BENAVIDEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>RUA</t>
+  </si>
+  <si>
+    <t>BERRIO GOMEZ</t>
+  </si>
+  <si>
+    <t>ROJAS CIFUENTES</t>
+  </si>
+  <si>
+    <t>PATIÑO ARANGO</t>
+  </si>
+  <si>
+    <t>ELENA IBARRA</t>
+  </si>
+  <si>
+    <t>CUARTAS RUIZ</t>
+  </si>
+  <si>
+    <t>CASTAÑO JIMENEZ</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ CASTAÑEDA</t>
+  </si>
+  <si>
+    <t>VICTORIA BERNAL</t>
+  </si>
+  <si>
+    <t>DE GUERRERO</t>
+  </si>
+  <si>
+    <t>LUZ BOTERO</t>
+  </si>
+  <si>
+    <t>GOMEZ LOPEZ</t>
+  </si>
+  <si>
+    <t>OROZCO VELASQUEZ</t>
+  </si>
+  <si>
+    <t>ZAPATA GONZALEZ</t>
+  </si>
+  <si>
+    <t>AGUDELO</t>
+  </si>
+  <si>
+    <t>GIRALDO GIRALDO</t>
+  </si>
+  <si>
+    <t>MARIN DUQUE</t>
+  </si>
+  <si>
+    <t>HENAO</t>
+  </si>
+  <si>
+    <t>OTALVARO OCHOA</t>
+  </si>
+  <si>
+    <t>RESTRICCIONES USUARIOS</t>
+  </si>
+  <si>
+    <t>P</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>BUITRAGO DIEZ</t>
+  </si>
+  <si>
+    <t>BALLEN</t>
+  </si>
+  <si>
+    <t>GARCIA O.</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>RENTERIA PALACIOS</t>
+  </si>
+  <si>
+    <t>CEBALLOS GIRALDO</t>
+  </si>
+  <si>
+    <t>ELENA USUGA</t>
+  </si>
+  <si>
+    <t>FIGUEROA</t>
+  </si>
+  <si>
+    <t>DAVID MARTINEZ</t>
+  </si>
+  <si>
+    <t>PAMPLONA MESA</t>
+  </si>
+  <si>
+    <t>VARGAS BANDA</t>
+  </si>
+  <si>
+    <t>MANUEL</t>
+  </si>
+  <si>
+    <t>MANUELA</t>
+  </si>
+  <si>
+    <t>MARCELA</t>
+  </si>
+  <si>
+    <t>MARIA ALEYDA</t>
+  </si>
+  <si>
+    <t>MARIA CARIDAD</t>
+  </si>
+  <si>
+    <t>MARIA CRISTINA</t>
+  </si>
+  <si>
+    <t>MARIA</t>
+  </si>
+  <si>
+    <t>MARIA ISABEL</t>
+  </si>
+  <si>
+    <t>MARIA NELLY</t>
+  </si>
+  <si>
+    <t>MARTHA ELENA RAMIREZ</t>
+  </si>
+  <si>
+    <t>MARTHA</t>
+  </si>
+  <si>
+    <t>MARY LUZ</t>
+  </si>
+  <si>
+    <t>MAURICIO</t>
+  </si>
+  <si>
+    <t>MAXIMILIANO</t>
+  </si>
+  <si>
+    <t>MIRIAM</t>
+  </si>
+  <si>
+    <t>OLGA AMPARO</t>
+  </si>
+  <si>
+    <t>OLGA NANCY</t>
+  </si>
+  <si>
+    <t>OLGA</t>
+  </si>
+  <si>
+    <t>PAOLA</t>
+  </si>
+  <si>
+    <t>PAULA</t>
+  </si>
+  <si>
+    <t>PIEDAD CECILIA</t>
+  </si>
+  <si>
+    <t>PRUEBA</t>
+  </si>
+  <si>
+    <t>RICARHD</t>
+  </si>
+  <si>
+    <t>RICHARD</t>
+  </si>
+  <si>
+    <t>SANDRA</t>
+  </si>
+  <si>
+    <t>SANDRA CECILIA</t>
+  </si>
+  <si>
+    <t>SARA</t>
+  </si>
+  <si>
+    <t>SOR MARIA</t>
+  </si>
+  <si>
+    <t>VANESSA</t>
+  </si>
+  <si>
+    <t>WALTER</t>
+  </si>
+  <si>
+    <t>YASMIN CECILIA</t>
+  </si>
+  <si>
+    <t>YASMIN</t>
+  </si>
+  <si>
+    <t>YOHANA</t>
+  </si>
+  <si>
+    <t>YULI</t>
+  </si>
+  <si>
+    <t>YULIANA MILEIDY</t>
+  </si>
+  <si>
+    <t>YULIANA</t>
+  </si>
+  <si>
+    <t>YURY MILENA</t>
+  </si>
+  <si>
+    <t>12111507</t>
+  </si>
+  <si>
+    <t>79820761</t>
+  </si>
+  <si>
+    <t>42071251</t>
+  </si>
+  <si>
+    <t>52081649</t>
+  </si>
+  <si>
+    <t>52865705</t>
+  </si>
+  <si>
+    <t>71719260</t>
+  </si>
+  <si>
+    <t>70829787</t>
+  </si>
+  <si>
+    <t>43063228</t>
+  </si>
+  <si>
+    <t>41787135</t>
+  </si>
+  <si>
+    <t>70903695</t>
+  </si>
+  <si>
+    <t>15423483</t>
+  </si>
+  <si>
+    <t>70826124</t>
+  </si>
+  <si>
+    <t>1040327042</t>
+  </si>
+  <si>
+    <t>30236956</t>
+  </si>
+  <si>
+    <t>8292913</t>
+  </si>
+  <si>
+    <t>70072053</t>
+  </si>
+  <si>
+    <t>70546842</t>
+  </si>
+  <si>
+    <t>1128264384</t>
+  </si>
+  <si>
+    <t>38794509</t>
+  </si>
+  <si>
+    <t>63502786</t>
+  </si>
+  <si>
+    <t>42098447</t>
+  </si>
+  <si>
+    <t>21374470</t>
+  </si>
+  <si>
+    <t>32511254</t>
+  </si>
+  <si>
+    <t>43059496</t>
+  </si>
+  <si>
+    <t>43053587</t>
+  </si>
+  <si>
+    <t>51843146</t>
+  </si>
+  <si>
+    <t>30712384</t>
+  </si>
+  <si>
+    <t>44002573</t>
+  </si>
+  <si>
+    <t>71645420</t>
+  </si>
+  <si>
+    <t>43644356</t>
+  </si>
+  <si>
+    <t>35336173</t>
+  </si>
+  <si>
+    <t>16266427</t>
+  </si>
+  <si>
+    <t>31575492</t>
+  </si>
+  <si>
+    <t>1045431905</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>3218302745</t>
+  </si>
+  <si>
+    <t>8772177</t>
+  </si>
+  <si>
+    <t>312977488</t>
+  </si>
+  <si>
+    <t>3117404287</t>
+  </si>
+  <si>
+    <t>3163654586</t>
+  </si>
+  <si>
+    <t>3117178575</t>
+  </si>
+  <si>
+    <t>3156310296</t>
+  </si>
+  <si>
+    <t>3135959014</t>
+  </si>
+  <si>
+    <t>3214942303</t>
+  </si>
+  <si>
+    <t>3115707502</t>
+  </si>
+  <si>
+    <t>3104789639</t>
+  </si>
+  <si>
+    <t>3204394759</t>
+  </si>
+  <si>
+    <t>3007501238</t>
+  </si>
+  <si>
+    <t>3006745512</t>
+  </si>
+  <si>
+    <t>3122397364</t>
+  </si>
+  <si>
+    <t>31306575450</t>
+  </si>
+  <si>
+    <t>3182822639</t>
+  </si>
+  <si>
+    <t>3103990065</t>
+  </si>
+  <si>
+    <t>3117490271</t>
+  </si>
+  <si>
+    <t>3148963783</t>
+  </si>
+  <si>
+    <t>3152136696</t>
+  </si>
+  <si>
+    <t>3007535977</t>
+  </si>
+  <si>
+    <t>31387705</t>
+  </si>
+  <si>
+    <t>3113065769</t>
+  </si>
+  <si>
+    <t>3008172967</t>
+  </si>
+  <si>
+    <t>3012408549</t>
+  </si>
+  <si>
+    <t>3103776152</t>
+  </si>
+  <si>
+    <t>3195612231</t>
+  </si>
+  <si>
+    <t>3206466832</t>
+  </si>
+  <si>
+    <t>3142951233</t>
+  </si>
+  <si>
+    <t>3234793172</t>
+  </si>
+  <si>
+    <t>3155094417</t>
+  </si>
+  <si>
+    <t>3192564608</t>
+  </si>
+  <si>
+    <t>3004839053</t>
+  </si>
+  <si>
+    <t>3164020098</t>
+  </si>
+  <si>
+    <t>3016008788</t>
+  </si>
+  <si>
+    <t>3127677561</t>
+  </si>
+  <si>
+    <t>30125010926</t>
+  </si>
+  <si>
+    <t>3153091207</t>
+  </si>
+  <si>
+    <t>3104361763</t>
+  </si>
+  <si>
+    <t>3105929120</t>
+  </si>
+  <si>
+    <t>3046280480</t>
+  </si>
+  <si>
+    <t>3165234752</t>
+  </si>
+  <si>
+    <t>3108327064</t>
+  </si>
+  <si>
+    <t>3186083418</t>
+  </si>
+  <si>
+    <t>3137861511</t>
+  </si>
+  <si>
+    <t>3128500320</t>
+  </si>
+  <si>
+    <t>3135040212</t>
+  </si>
+  <si>
+    <t>3217699480</t>
+  </si>
+  <si>
+    <t>3127843385</t>
+  </si>
+  <si>
+    <t>3113132826</t>
+  </si>
+  <si>
+    <t>3188679009</t>
+  </si>
+  <si>
+    <t>3104752087</t>
+  </si>
+  <si>
+    <t>6044485757</t>
+  </si>
+  <si>
+    <t>2514896</t>
+  </si>
+  <si>
+    <t>3017564610</t>
+  </si>
+  <si>
+    <t>3012125884</t>
+  </si>
+  <si>
+    <t>3113334943</t>
+  </si>
+  <si>
+    <t>3146177302</t>
+  </si>
+  <si>
+    <t>3174005371</t>
+  </si>
+  <si>
+    <t>3506738710</t>
+  </si>
+  <si>
+    <t>3226565603</t>
+  </si>
+  <si>
+    <t>3137446066</t>
+  </si>
+  <si>
+    <t>3106435930</t>
+  </si>
+  <si>
+    <t>3013879673</t>
+  </si>
+  <si>
+    <t>3013149038</t>
+  </si>
+  <si>
+    <t>OFICINA, OFICINA</t>
+  </si>
+  <si>
+    <t>PERSONAL, OFICINA</t>
+  </si>
+  <si>
+    <t>3502448164,</t>
+  </si>
+  <si>
+    <t>contabilidad@plasticosgyc.com</t>
+  </si>
+  <si>
+    <t>aabdel@sura.com.co</t>
+  </si>
+  <si>
+    <t>amarin@sedic.com.co</t>
+  </si>
+  <si>
+    <t>direccionadministrativa@corpoases.com.co</t>
+  </si>
+  <si>
+    <t>abonilla@sena.edu.co</t>
+  </si>
+  <si>
+    <t>alvis.vasquez@udea.edu.co</t>
+  </si>
+  <si>
+    <t>Anajaramillo@abacoadjusters.com</t>
+  </si>
+  <si>
+    <t>colimaasociados@hotmail.com</t>
+  </si>
+  <si>
+    <t>juridico@grupoantc.com</t>
+  </si>
+  <si>
+    <t>lmhincapiel@gmail.com</t>
+  </si>
+  <si>
+    <t>beatrizvalencia@coosanroque.com</t>
+  </si>
+  <si>
+    <t>Secretariasecretariaacademica.znorte@gmail.com</t>
+  </si>
+  <si>
+    <t>carolina.munoz@atheneasoluciones.com</t>
+  </si>
+  <si>
+    <t>rmartinezc@misena.edu.co;rmartinezc@misena.edu.co</t>
+  </si>
+  <si>
+    <t>contabilidad@cpsih.edu.co</t>
+  </si>
+  <si>
+    <t>administrador@industrypartes.com</t>
+  </si>
+  <si>
+    <t>dirinfancia@fundacionlasgolondrinas.org</t>
+  </si>
+  <si>
+    <t>administracion@compropano.co</t>
+  </si>
+  <si>
+    <t>secretariacorpobosques1@gmail.com</t>
+  </si>
+  <si>
+    <t>cpatrillan@eycglobal.com</t>
+  </si>
+  <si>
+    <t>dlopez@9division.com</t>
+  </si>
+  <si>
+    <t>ebusta2310@gmail.com</t>
+  </si>
+  <si>
+    <t>contabilidad@sanjuan.com.co</t>
+  </si>
+  <si>
+    <t>comercial@transportesmultimodales.com</t>
+  </si>
+  <si>
+    <t>giovanniocampo79@hotmail.com</t>
+  </si>
+  <si>
+    <t>gloriam37@gmail.com</t>
+  </si>
+  <si>
+    <t>gtruiz01@yahoo.es</t>
+  </si>
+  <si>
+    <t>gcarvajal@sena.edu.co</t>
+  </si>
+  <si>
+    <t>hector.cruz@riskclaims.com.co</t>
+  </si>
+  <si>
+    <t>hagarciag6@gmail.com</t>
+  </si>
+  <si>
+    <t>tesoreria@iumafis.edu.co</t>
+  </si>
+  <si>
+    <t>isabelaguirrealvarez.fla@gmail.com</t>
+  </si>
+  <si>
+    <t>CALIDAD@CERI.EDU.CO</t>
+  </si>
+  <si>
+    <t>ivaucasa@gmail.com</t>
+  </si>
+  <si>
+    <t>jeninorena@hotmail.com</t>
+  </si>
+  <si>
+    <t>jennyreyes05@yahoo.com</t>
+  </si>
+  <si>
+    <t>MARJOLOGISTICA@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>gloriaearisti@gmail.com</t>
+  </si>
+  <si>
+    <t>JUANVELEZ54@HOTMAIL.COM</t>
+  </si>
+  <si>
+    <t>gerencia.transnus@gmail.com</t>
+  </si>
+  <si>
+    <t>Santiriversan07@gmail.com</t>
+  </si>
+  <si>
+    <t>Juanolartem@hotmail.com</t>
+  </si>
+  <si>
+    <t>directoradmin@grupoantc.com</t>
+  </si>
+  <si>
+    <t>makicenter01@hotmail.com</t>
+  </si>
+  <si>
+    <t>Ktcossio@hotmail.com</t>
+  </si>
+  <si>
+    <t>ventas@metalicas2000.com</t>
+  </si>
+  <si>
+    <t>loren_arc@yahoo.com</t>
+  </si>
+  <si>
+    <t>vfaingenieriasas@vfaingenieria.com</t>
+  </si>
+  <si>
+    <t>luzdaflo@gmail.com</t>
+  </si>
+  <si>
+    <t>transnussas@gmail.com</t>
+  </si>
+  <si>
+    <t>lsmartinezo2870@hotmail.com</t>
+  </si>
+  <si>
+    <t>Gerencia@telodijecomunicaciones.com</t>
+  </si>
+  <si>
+    <t>asistenteadministrativo@trosorio.com</t>
+  </si>
+  <si>
+    <t>linamarcela-a@hotmail.com</t>
+  </si>
+  <si>
+    <t>mpatino@sedic.com.co</t>
+  </si>
+  <si>
+    <t>TALENTOHUMANO@FSJB.CO</t>
+  </si>
+  <si>
+    <t>nelurac@hotmail.com</t>
+  </si>
+  <si>
+    <t>mrodriguez@rotrasvehi.com</t>
+  </si>
+  <si>
+    <t>ramirezlopezmarthaelena@gmail.com</t>
+  </si>
+  <si>
+    <t>direccionadministrativa@gimnasiocantabria.Edu.co</t>
+  </si>
+  <si>
+    <t>maryluz.gomez85@gmail.com</t>
+  </si>
+  <si>
+    <t>secretaria@esetitiribi.gov.co</t>
+  </si>
+  <si>
+    <t>olgagiraldo672@gmail.com</t>
+  </si>
+  <si>
+    <t>olmadu@hotmail.com</t>
+  </si>
+  <si>
+    <t>piedadotalvaro@hotmail.com</t>
+  </si>
+  <si>
+    <t>richardpub@yahoo.com</t>
+  </si>
+  <si>
+    <t>AUXADMINISTARTIVO@INDUSTRYPARTES.COM</t>
+  </si>
+  <si>
+    <t>compras@metalicas2000.com</t>
+  </si>
+  <si>
+    <t>vgonzalez@eycglobal.com</t>
+  </si>
+  <si>
+    <t>wrenteria@misena.edu.co</t>
+  </si>
+  <si>
+    <t>yceballosg@hotmail.es</t>
+  </si>
+  <si>
+    <t>calidad@metrocert.com.co</t>
+  </si>
+  <si>
+    <t>comufa@hotmail.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3457,8 +4636,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3467,18 +4651,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF3E63E7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -3501,6 +4679,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -3510,8 +4703,8 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3817,35 +5010,47 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AN1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AN120"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="40" width="17.7109375" customWidth="1"/>
+    <col min="1" max="1" width="20.140625" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="3" width="29.7109375" customWidth="1"/>
+    <col min="4" max="4" width="29.5703125" customWidth="1"/>
+    <col min="5" max="5" width="17.7109375" customWidth="1"/>
+    <col min="6" max="6" width="9.140625"/>
+    <col min="7" max="8" width="17.7109375" customWidth="1"/>
+    <col min="9" max="9" width="21" customWidth="1"/>
+    <col min="10" max="10" width="19.7109375" customWidth="1"/>
+    <col min="11" max="14" width="17.7109375" customWidth="1"/>
+    <col min="15" max="15" width="28.7109375" customWidth="1"/>
+    <col min="16" max="16" width="26.42578125" customWidth="1"/>
+    <col min="17" max="40" width="17.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:40" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="2" t="s">
@@ -3854,16 +5059,16 @@
       <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
       <c r="O1" s="2" t="s">
@@ -3872,77 +5077,2781 @@
       <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="V1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="W1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="X1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="Y1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AA1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AB1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AC1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AD1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="2" t="s">
+      <c r="AE1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="2" t="s">
+      <c r="AF1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="2" t="s">
+      <c r="AG1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="2" t="s">
+      <c r="AH1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="2" t="s">
+      <c r="AI1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="2" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="2" t="s">
+      <c r="AK1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="2" t="s">
+      <c r="AL1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="2" t="s">
+      <c r="AM1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" s="2" t="s">
+      <c r="AN1" s="1" t="s">
         <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1126</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1191</v>
+      </c>
+      <c r="E2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F2" t="s">
+        <v>1374</v>
+      </c>
+      <c r="O2" t="s">
+        <v>1446</v>
+      </c>
+      <c r="P2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1192</v>
+      </c>
+      <c r="E3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F3" t="s">
+        <v>1374</v>
+      </c>
+      <c r="O3" t="s">
+        <v>1447</v>
+      </c>
+      <c r="P3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>1128</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1193</v>
+      </c>
+      <c r="E4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F4" t="s">
+        <v>1375</v>
+      </c>
+      <c r="I4" t="s">
+        <v>1445</v>
+      </c>
+      <c r="J4" t="s">
+        <v>56</v>
+      </c>
+      <c r="O4" t="s">
+        <v>1448</v>
+      </c>
+      <c r="P4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>1128</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1194</v>
+      </c>
+      <c r="E5" t="s">
+        <v>40</v>
+      </c>
+      <c r="F5" t="s">
+        <v>1374</v>
+      </c>
+      <c r="I5" t="s">
+        <v>1377</v>
+      </c>
+      <c r="J5" t="s">
+        <v>56</v>
+      </c>
+      <c r="O5" t="s">
+        <v>1449</v>
+      </c>
+      <c r="P5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>1129</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1195</v>
+      </c>
+      <c r="D6" t="s">
+        <v>1340</v>
+      </c>
+      <c r="E6" t="s">
+        <v>40</v>
+      </c>
+      <c r="F6" t="s">
+        <v>1374</v>
+      </c>
+      <c r="I6" t="s">
+        <v>1378</v>
+      </c>
+      <c r="J6" t="s">
+        <v>55</v>
+      </c>
+      <c r="O6" t="s">
+        <v>1450</v>
+      </c>
+      <c r="P6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1196</v>
+      </c>
+      <c r="E7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F7" t="s">
+        <v>1375</v>
+      </c>
+      <c r="I7" t="s">
+        <v>1379</v>
+      </c>
+      <c r="J7" t="s">
+        <v>55</v>
+      </c>
+      <c r="O7" t="s">
+        <v>1451</v>
+      </c>
+      <c r="P7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>1131</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1197</v>
+      </c>
+      <c r="E8" t="s">
+        <v>40</v>
+      </c>
+      <c r="F8" t="s">
+        <v>1374</v>
+      </c>
+      <c r="I8" t="s">
+        <v>1380</v>
+      </c>
+      <c r="J8" t="s">
+        <v>55</v>
+      </c>
+      <c r="O8" t="s">
+        <v>1452</v>
+      </c>
+      <c r="P8" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>1132</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1198</v>
+      </c>
+      <c r="E9" t="s">
+        <v>40</v>
+      </c>
+      <c r="F9" t="s">
+        <v>1374</v>
+      </c>
+      <c r="I9" t="s">
+        <v>1381</v>
+      </c>
+      <c r="J9" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1199</v>
+      </c>
+      <c r="E10" t="s">
+        <v>40</v>
+      </c>
+      <c r="F10" t="s">
+        <v>1375</v>
+      </c>
+    </row>
+    <row r="11" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>1134</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1200</v>
+      </c>
+      <c r="E11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F11" t="s">
+        <v>1375</v>
+      </c>
+    </row>
+    <row r="12" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>1135</v>
+      </c>
+      <c r="B12" t="s">
+        <v>1201</v>
+      </c>
+      <c r="D12" t="s">
+        <v>1341</v>
+      </c>
+      <c r="E12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F12" t="s">
+        <v>1374</v>
+      </c>
+    </row>
+    <row r="13" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>1136</v>
+      </c>
+      <c r="B13" t="s">
+        <v>1202</v>
+      </c>
+      <c r="E13" t="s">
+        <v>40</v>
+      </c>
+      <c r="F13" t="s">
+        <v>1376</v>
+      </c>
+      <c r="I13" t="s">
+        <v>1382</v>
+      </c>
+      <c r="J13" t="s">
+        <v>56</v>
+      </c>
+      <c r="O13" t="s">
+        <v>1453</v>
+      </c>
+      <c r="P13" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B14" t="s">
+        <v>1203</v>
+      </c>
+      <c r="E14" t="s">
+        <v>40</v>
+      </c>
+      <c r="F14" t="s">
+        <v>1375</v>
+      </c>
+      <c r="I14" t="s">
+        <v>1383</v>
+      </c>
+      <c r="J14" t="s">
+        <v>55</v>
+      </c>
+      <c r="O14" t="s">
+        <v>1454</v>
+      </c>
+      <c r="P14" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="15" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>1138</v>
+      </c>
+      <c r="B15" t="s">
+        <v>1204</v>
+      </c>
+      <c r="D15" t="s">
+        <v>1342</v>
+      </c>
+      <c r="E15" t="s">
+        <v>40</v>
+      </c>
+      <c r="F15" t="s">
+        <v>1375</v>
+      </c>
+      <c r="O15" t="s">
+        <v>1455</v>
+      </c>
+      <c r="P15" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="16" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>1139</v>
+      </c>
+      <c r="B16" t="s">
+        <v>594</v>
+      </c>
+      <c r="E16" t="s">
+        <v>40</v>
+      </c>
+      <c r="F16" t="s">
+        <v>1374</v>
+      </c>
+      <c r="I16" t="s">
+        <v>1384</v>
+      </c>
+      <c r="J16" t="s">
+        <v>56</v>
+      </c>
+      <c r="O16" t="s">
+        <v>1456</v>
+      </c>
+      <c r="P16" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>1140</v>
+      </c>
+      <c r="B17" t="s">
+        <v>1205</v>
+      </c>
+      <c r="D17" t="s">
+        <v>1343</v>
+      </c>
+      <c r="E17" t="s">
+        <v>40</v>
+      </c>
+      <c r="F17" t="s">
+        <v>1375</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B18" t="s">
+        <v>1206</v>
+      </c>
+      <c r="E18" t="s">
+        <v>40</v>
+      </c>
+      <c r="F18" t="s">
+        <v>1374</v>
+      </c>
+      <c r="I18" t="s">
+        <v>1385</v>
+      </c>
+      <c r="J18" t="s">
+        <v>55</v>
+      </c>
+      <c r="O18" t="s">
+        <v>1457</v>
+      </c>
+      <c r="P18" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>132</v>
+      </c>
+      <c r="B19" t="s">
+        <v>1207</v>
+      </c>
+      <c r="E19" t="s">
+        <v>40</v>
+      </c>
+      <c r="F19" t="s">
+        <v>1374</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>132</v>
+      </c>
+      <c r="B20" t="s">
+        <v>1208</v>
+      </c>
+      <c r="E20" t="s">
+        <v>40</v>
+      </c>
+      <c r="F20" t="s">
+        <v>1374</v>
+      </c>
+      <c r="I20" t="s">
+        <v>1386</v>
+      </c>
+      <c r="J20" t="s">
+        <v>55</v>
+      </c>
+      <c r="O20" t="s">
+        <v>1458</v>
+      </c>
+      <c r="P20" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>132</v>
+      </c>
+      <c r="B21" t="s">
+        <v>1209</v>
+      </c>
+      <c r="E21" t="s">
+        <v>40</v>
+      </c>
+      <c r="F21" t="s">
+        <v>1374</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>1142</v>
+      </c>
+      <c r="B22" t="s">
+        <v>1210</v>
+      </c>
+      <c r="E22" t="s">
+        <v>40</v>
+      </c>
+      <c r="F22" t="s">
+        <v>1374</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B23" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D23" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E23" t="s">
+        <v>40</v>
+      </c>
+      <c r="F23" t="s">
+        <v>1374</v>
+      </c>
+      <c r="I23" t="s">
+        <v>1387</v>
+      </c>
+      <c r="J23" t="s">
+        <v>55</v>
+      </c>
+      <c r="O23" t="s">
+        <v>1459</v>
+      </c>
+      <c r="P23" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B24" t="s">
+        <v>1212</v>
+      </c>
+      <c r="E24" t="s">
+        <v>40</v>
+      </c>
+      <c r="F24" t="s">
+        <v>1374</v>
+      </c>
+      <c r="I24" t="s">
+        <v>1388</v>
+      </c>
+      <c r="J24" t="s">
+        <v>56</v>
+      </c>
+      <c r="O24" t="s">
+        <v>1460</v>
+      </c>
+      <c r="P24" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B25" t="s">
+        <v>1213</v>
+      </c>
+      <c r="E25" t="s">
+        <v>40</v>
+      </c>
+      <c r="F25" t="s">
+        <v>1375</v>
+      </c>
+      <c r="I25" t="s">
+        <v>1389</v>
+      </c>
+      <c r="J25" t="s">
+        <v>55</v>
+      </c>
+      <c r="O25" t="s">
+        <v>1461</v>
+      </c>
+      <c r="P25" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B26" t="s">
+        <v>1214</v>
+      </c>
+      <c r="E26" t="s">
+        <v>40</v>
+      </c>
+      <c r="F26" t="s">
+        <v>1374</v>
+      </c>
+      <c r="I26" t="s">
+        <v>1390</v>
+      </c>
+      <c r="J26" t="s">
+        <v>55</v>
+      </c>
+      <c r="O26" t="s">
+        <v>1462</v>
+      </c>
+      <c r="P26" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>1146</v>
+      </c>
+      <c r="B27" t="s">
+        <v>1215</v>
+      </c>
+      <c r="E27" t="s">
+        <v>40</v>
+      </c>
+      <c r="F27" t="s">
+        <v>1375</v>
+      </c>
+      <c r="I27">
+        <v>3107617908</v>
+      </c>
+      <c r="J27" t="s">
+        <v>56</v>
+      </c>
+      <c r="O27" t="s">
+        <v>1463</v>
+      </c>
+      <c r="P27" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>1147</v>
+      </c>
+      <c r="B28" t="s">
+        <v>1216</v>
+      </c>
+      <c r="E28" t="s">
+        <v>40</v>
+      </c>
+      <c r="F28" t="s">
+        <v>1374</v>
+      </c>
+      <c r="I28" t="s">
+        <v>1391</v>
+      </c>
+      <c r="J28" t="s">
+        <v>56</v>
+      </c>
+      <c r="O28" t="s">
+        <v>1464</v>
+      </c>
+      <c r="P28" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B29" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E29" t="s">
+        <v>40</v>
+      </c>
+      <c r="F29" t="s">
+        <v>1374</v>
+      </c>
+      <c r="O29" t="s">
+        <v>1465</v>
+      </c>
+      <c r="P29" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>1149</v>
+      </c>
+      <c r="B30" t="s">
+        <v>1218</v>
+      </c>
+      <c r="E30" t="s">
+        <v>40</v>
+      </c>
+      <c r="F30" t="s">
+        <v>1374</v>
+      </c>
+      <c r="I30" t="s">
+        <v>1392</v>
+      </c>
+      <c r="J30" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>1150</v>
+      </c>
+      <c r="B31" t="s">
+        <v>1219</v>
+      </c>
+      <c r="E31" t="s">
+        <v>40</v>
+      </c>
+      <c r="F31" t="s">
+        <v>1374</v>
+      </c>
+      <c r="I31" t="s">
+        <v>1393</v>
+      </c>
+      <c r="J31" t="s">
+        <v>55</v>
+      </c>
+      <c r="O31" t="s">
+        <v>1466</v>
+      </c>
+      <c r="P31" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B32" t="s">
+        <v>1220</v>
+      </c>
+      <c r="E32" t="s">
+        <v>40</v>
+      </c>
+      <c r="F32" t="s">
+        <v>1374</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B33" t="s">
+        <v>1221</v>
+      </c>
+      <c r="D33" t="s">
+        <v>1345</v>
+      </c>
+      <c r="E33" t="s">
+        <v>40</v>
+      </c>
+      <c r="F33" t="s">
+        <v>1374</v>
+      </c>
+      <c r="I33" t="s">
+        <v>1394</v>
+      </c>
+      <c r="J33" t="s">
+        <v>55</v>
+      </c>
+      <c r="O33" t="s">
+        <v>1467</v>
+      </c>
+      <c r="P33" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>1153</v>
+      </c>
+      <c r="B34" t="s">
+        <v>1222</v>
+      </c>
+      <c r="E34" t="s">
+        <v>40</v>
+      </c>
+      <c r="F34" t="s">
+        <v>1374</v>
+      </c>
+      <c r="O34" t="s">
+        <v>1468</v>
+      </c>
+      <c r="P34" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>1154</v>
+      </c>
+      <c r="B35" t="s">
+        <v>1223</v>
+      </c>
+      <c r="E35" t="s">
+        <v>40</v>
+      </c>
+      <c r="F35" t="s">
+        <v>1374</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>1155</v>
+      </c>
+      <c r="B36" t="s">
+        <v>1224</v>
+      </c>
+      <c r="E36" t="s">
+        <v>40</v>
+      </c>
+      <c r="F36" t="s">
+        <v>1375</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B37" t="s">
+        <v>1225</v>
+      </c>
+      <c r="E37" t="s">
+        <v>40</v>
+      </c>
+      <c r="F37" t="s">
+        <v>1375</v>
+      </c>
+      <c r="I37" t="s">
+        <v>1395</v>
+      </c>
+      <c r="J37" t="s">
+        <v>55</v>
+      </c>
+      <c r="O37" t="s">
+        <v>1469</v>
+      </c>
+      <c r="P37" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B38" t="s">
+        <v>1226</v>
+      </c>
+      <c r="E38" t="s">
+        <v>40</v>
+      </c>
+      <c r="F38" t="s">
+        <v>1374</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B39" t="s">
+        <v>1227</v>
+      </c>
+      <c r="D39" t="s">
+        <v>1346</v>
+      </c>
+      <c r="E39" t="s">
+        <v>40</v>
+      </c>
+      <c r="F39" t="s">
+        <v>1375</v>
+      </c>
+      <c r="I39">
+        <v>3136145830</v>
+      </c>
+      <c r="J39" t="s">
+        <v>1444</v>
+      </c>
+      <c r="O39" t="s">
+        <v>1470</v>
+      </c>
+      <c r="P39" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>1159</v>
+      </c>
+      <c r="B40" t="s">
+        <v>1228</v>
+      </c>
+      <c r="D40" t="s">
+        <v>1347</v>
+      </c>
+      <c r="E40" t="s">
+        <v>40</v>
+      </c>
+      <c r="F40" t="s">
+        <v>1374</v>
+      </c>
+      <c r="I40" t="s">
+        <v>1396</v>
+      </c>
+      <c r="J40" t="s">
+        <v>55</v>
+      </c>
+      <c r="O40" t="s">
+        <v>1471</v>
+      </c>
+      <c r="P40" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>1160</v>
+      </c>
+      <c r="B41" t="s">
+        <v>1229</v>
+      </c>
+      <c r="D41" t="s">
+        <v>1348</v>
+      </c>
+      <c r="E41" t="s">
+        <v>40</v>
+      </c>
+      <c r="F41" t="s">
+        <v>1374</v>
+      </c>
+      <c r="I41" t="s">
+        <v>1397</v>
+      </c>
+      <c r="J41" t="s">
+        <v>55</v>
+      </c>
+      <c r="O41" t="s">
+        <v>1472</v>
+      </c>
+      <c r="P41" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B42" t="s">
+        <v>1230</v>
+      </c>
+      <c r="D42" t="s">
+        <v>1349</v>
+      </c>
+      <c r="E42" t="s">
+        <v>40</v>
+      </c>
+      <c r="F42" t="s">
+        <v>1375</v>
+      </c>
+      <c r="I42" t="s">
+        <v>1398</v>
+      </c>
+      <c r="J42" t="s">
+        <v>55</v>
+      </c>
+      <c r="O42" t="s">
+        <v>1473</v>
+      </c>
+      <c r="P42" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>1162</v>
+      </c>
+      <c r="B43" t="s">
+        <v>1231</v>
+      </c>
+      <c r="E43" t="s">
+        <v>40</v>
+      </c>
+      <c r="F43" t="s">
+        <v>1374</v>
+      </c>
+      <c r="I43" t="s">
+        <v>1399</v>
+      </c>
+      <c r="J43" t="s">
+        <v>56</v>
+      </c>
+      <c r="O43" t="s">
+        <v>1474</v>
+      </c>
+      <c r="P43" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>1163</v>
+      </c>
+      <c r="B44" t="s">
+        <v>1232</v>
+      </c>
+      <c r="D44" t="s">
+        <v>1350</v>
+      </c>
+      <c r="E44" t="s">
+        <v>40</v>
+      </c>
+      <c r="F44" t="s">
+        <v>1375</v>
+      </c>
+      <c r="I44" t="s">
+        <v>1400</v>
+      </c>
+      <c r="J44" t="s">
+        <v>55</v>
+      </c>
+      <c r="O44" t="s">
+        <v>1475</v>
+      </c>
+      <c r="P44" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>1164</v>
+      </c>
+      <c r="B45" t="s">
+        <v>1233</v>
+      </c>
+      <c r="E45" t="s">
+        <v>40</v>
+      </c>
+      <c r="F45" t="s">
+        <v>1374</v>
+      </c>
+      <c r="I45" t="s">
+        <v>1401</v>
+      </c>
+      <c r="J45" t="s">
+        <v>55</v>
+      </c>
+      <c r="O45" t="s">
+        <v>1476</v>
+      </c>
+      <c r="P45" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>1165</v>
+      </c>
+      <c r="B46" t="s">
+        <v>1234</v>
+      </c>
+      <c r="E46" t="s">
+        <v>40</v>
+      </c>
+      <c r="F46" t="s">
+        <v>1374</v>
+      </c>
+      <c r="I46">
+        <v>3004850864</v>
+      </c>
+      <c r="J46" t="s">
+        <v>56</v>
+      </c>
+      <c r="O46" t="s">
+        <v>1477</v>
+      </c>
+      <c r="P46" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>1165</v>
+      </c>
+      <c r="B47" t="s">
+        <v>1235</v>
+      </c>
+      <c r="E47" t="s">
+        <v>40</v>
+      </c>
+      <c r="F47" t="s">
+        <v>1374</v>
+      </c>
+      <c r="I47" t="s">
+        <v>1402</v>
+      </c>
+      <c r="J47" t="s">
+        <v>55</v>
+      </c>
+      <c r="O47" t="s">
+        <v>1478</v>
+      </c>
+      <c r="P47" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>1166</v>
+      </c>
+      <c r="B48" t="s">
+        <v>1236</v>
+      </c>
+      <c r="D48" t="s">
+        <v>1351</v>
+      </c>
+      <c r="E48" t="s">
+        <v>40</v>
+      </c>
+      <c r="F48" t="s">
+        <v>1375</v>
+      </c>
+      <c r="I48" t="s">
+        <v>1403</v>
+      </c>
+      <c r="J48" t="s">
+        <v>55</v>
+      </c>
+      <c r="O48" t="s">
+        <v>1479</v>
+      </c>
+      <c r="P48" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B49" t="s">
+        <v>1237</v>
+      </c>
+      <c r="E49" t="s">
+        <v>40</v>
+      </c>
+      <c r="F49" t="s">
+        <v>1374</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>1168</v>
+      </c>
+      <c r="B50" t="s">
+        <v>1238</v>
+      </c>
+      <c r="E50" t="s">
+        <v>40</v>
+      </c>
+      <c r="F50" t="s">
+        <v>1374</v>
+      </c>
+      <c r="I50" t="s">
+        <v>1404</v>
+      </c>
+      <c r="J50" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B51" t="s">
+        <v>1239</v>
+      </c>
+      <c r="E51" t="s">
+        <v>40</v>
+      </c>
+      <c r="F51" t="s">
+        <v>1374</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>1170</v>
+      </c>
+      <c r="B52" t="s">
+        <v>1240</v>
+      </c>
+      <c r="D52" t="s">
+        <v>1352</v>
+      </c>
+      <c r="E52" t="s">
+        <v>40</v>
+      </c>
+      <c r="F52" t="s">
+        <v>1374</v>
+      </c>
+      <c r="I52" t="s">
+        <v>1405</v>
+      </c>
+      <c r="J52" t="s">
+        <v>55</v>
+      </c>
+      <c r="O52" t="s">
+        <v>1480</v>
+      </c>
+      <c r="P52" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>1171</v>
+      </c>
+      <c r="B53" t="s">
+        <v>1241</v>
+      </c>
+      <c r="E53" t="s">
+        <v>40</v>
+      </c>
+      <c r="F53" t="s">
+        <v>1374</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>1172</v>
+      </c>
+      <c r="B54" t="s">
+        <v>1242</v>
+      </c>
+      <c r="D54" t="s">
+        <v>1353</v>
+      </c>
+      <c r="E54" t="s">
+        <v>40</v>
+      </c>
+      <c r="F54" t="s">
+        <v>1374</v>
+      </c>
+      <c r="I54" t="s">
+        <v>1406</v>
+      </c>
+      <c r="J54" t="s">
+        <v>55</v>
+      </c>
+      <c r="O54" t="s">
+        <v>1481</v>
+      </c>
+      <c r="P54" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>1173</v>
+      </c>
+      <c r="B55" t="s">
+        <v>1243</v>
+      </c>
+      <c r="E55" t="s">
+        <v>40</v>
+      </c>
+      <c r="F55" t="s">
+        <v>1374</v>
+      </c>
+      <c r="I55" t="s">
+        <v>1407</v>
+      </c>
+      <c r="J55" t="s">
+        <v>56</v>
+      </c>
+      <c r="O55" t="s">
+        <v>1482</v>
+      </c>
+      <c r="P55" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B56" t="s">
+        <v>1244</v>
+      </c>
+      <c r="E56" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>1175</v>
+      </c>
+      <c r="B57" t="s">
+        <v>1245</v>
+      </c>
+      <c r="E57" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B58" t="s">
+        <v>1246</v>
+      </c>
+      <c r="D58" t="s">
+        <v>1354</v>
+      </c>
+      <c r="E58" t="s">
+        <v>40</v>
+      </c>
+      <c r="F58" t="s">
+        <v>1374</v>
+      </c>
+      <c r="I58">
+        <v>3005591801</v>
+      </c>
+      <c r="J58" t="s">
+        <v>56</v>
+      </c>
+      <c r="O58" t="s">
+        <v>1483</v>
+      </c>
+      <c r="P58" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>1177</v>
+      </c>
+      <c r="B59" t="s">
+        <v>1247</v>
+      </c>
+      <c r="D59" t="s">
+        <v>1355</v>
+      </c>
+      <c r="E59" t="s">
+        <v>40</v>
+      </c>
+      <c r="F59" t="s">
+        <v>1375</v>
+      </c>
+      <c r="I59" t="s">
+        <v>1408</v>
+      </c>
+      <c r="J59" t="s">
+        <v>55</v>
+      </c>
+      <c r="O59" t="s">
+        <v>1484</v>
+      </c>
+      <c r="P59" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>1178</v>
+      </c>
+      <c r="B60" t="s">
+        <v>1248</v>
+      </c>
+      <c r="E60" t="s">
+        <v>40</v>
+      </c>
+      <c r="F60" t="s">
+        <v>1374</v>
+      </c>
+      <c r="I60" t="s">
+        <v>1409</v>
+      </c>
+      <c r="J60" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>1178</v>
+      </c>
+      <c r="B61" t="s">
+        <v>1249</v>
+      </c>
+      <c r="E61" t="s">
+        <v>40</v>
+      </c>
+      <c r="F61" t="s">
+        <v>1374</v>
+      </c>
+      <c r="I61" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J61" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>1179</v>
+      </c>
+      <c r="B62" t="s">
+        <v>1250</v>
+      </c>
+      <c r="E62" t="s">
+        <v>40</v>
+      </c>
+      <c r="F62" t="s">
+        <v>1374</v>
+      </c>
+      <c r="I62">
+        <v>3183743820</v>
+      </c>
+      <c r="J62" t="s">
+        <v>56</v>
+      </c>
+      <c r="O62" t="s">
+        <v>1485</v>
+      </c>
+      <c r="P62" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>1180</v>
+      </c>
+      <c r="B63" t="s">
+        <v>1251</v>
+      </c>
+      <c r="D63" t="s">
+        <v>1356</v>
+      </c>
+      <c r="E63" t="s">
+        <v>40</v>
+      </c>
+      <c r="F63" t="s">
+        <v>1374</v>
+      </c>
+      <c r="I63" t="s">
+        <v>1411</v>
+      </c>
+      <c r="J63" t="s">
+        <v>55</v>
+      </c>
+      <c r="O63" t="s">
+        <v>1486</v>
+      </c>
+      <c r="P63" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>1178</v>
+      </c>
+      <c r="B64" t="s">
+        <v>1252</v>
+      </c>
+      <c r="E64" t="s">
+        <v>40</v>
+      </c>
+      <c r="F64" t="s">
+        <v>1374</v>
+      </c>
+      <c r="I64" t="s">
+        <v>1412</v>
+      </c>
+      <c r="J64" t="s">
+        <v>55</v>
+      </c>
+      <c r="O64" t="s">
+        <v>1487</v>
+      </c>
+      <c r="P64" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>1178</v>
+      </c>
+      <c r="B65" t="s">
+        <v>1253</v>
+      </c>
+      <c r="E65" t="s">
+        <v>40</v>
+      </c>
+      <c r="F65" t="s">
+        <v>1375</v>
+      </c>
+      <c r="I65">
+        <v>3164467780</v>
+      </c>
+      <c r="J65" t="s">
+        <v>56</v>
+      </c>
+      <c r="O65" t="s">
+        <v>1488</v>
+      </c>
+      <c r="P65" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>1178</v>
+      </c>
+      <c r="B66" t="s">
+        <v>1253</v>
+      </c>
+      <c r="E66" t="s">
+        <v>40</v>
+      </c>
+      <c r="F66" t="s">
+        <v>1375</v>
+      </c>
+      <c r="I66">
+        <v>3164467780</v>
+      </c>
+      <c r="J66" t="s">
+        <v>1443</v>
+      </c>
+      <c r="O66" t="s">
+        <v>1488</v>
+      </c>
+      <c r="P66" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>1178</v>
+      </c>
+      <c r="B67" t="s">
+        <v>1254</v>
+      </c>
+      <c r="E67" t="s">
+        <v>40</v>
+      </c>
+      <c r="F67" t="s">
+        <v>1374</v>
+      </c>
+      <c r="I67" t="s">
+        <v>1413</v>
+      </c>
+      <c r="J67" t="s">
+        <v>56</v>
+      </c>
+      <c r="O67" t="s">
+        <v>1489</v>
+      </c>
+      <c r="P67" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B68" t="s">
+        <v>1255</v>
+      </c>
+      <c r="D68" t="s">
+        <v>1357</v>
+      </c>
+      <c r="E68" t="s">
+        <v>40</v>
+      </c>
+      <c r="F68" t="s">
+        <v>1374</v>
+      </c>
+      <c r="I68" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J68" t="s">
+        <v>55</v>
+      </c>
+      <c r="O68" t="s">
+        <v>1490</v>
+      </c>
+      <c r="P68" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>1182</v>
+      </c>
+      <c r="B69" t="s">
+        <v>1256</v>
+      </c>
+      <c r="E69" t="s">
+        <v>40</v>
+      </c>
+      <c r="F69" t="s">
+        <v>1374</v>
+      </c>
+    </row>
+    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>1183</v>
+      </c>
+      <c r="B70" t="s">
+        <v>1257</v>
+      </c>
+      <c r="E70" t="s">
+        <v>40</v>
+      </c>
+      <c r="F70" t="s">
+        <v>1374</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>1184</v>
+      </c>
+      <c r="B71" t="s">
+        <v>1258</v>
+      </c>
+      <c r="E71" t="s">
+        <v>40</v>
+      </c>
+      <c r="F71" t="s">
+        <v>1374</v>
+      </c>
+      <c r="I71">
+        <v>3206680047</v>
+      </c>
+      <c r="J71" t="s">
+        <v>1443</v>
+      </c>
+      <c r="O71" t="s">
+        <v>1491</v>
+      </c>
+      <c r="P71" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>1184</v>
+      </c>
+      <c r="B72" t="s">
+        <v>1259</v>
+      </c>
+      <c r="E72" t="s">
+        <v>40</v>
+      </c>
+      <c r="F72" t="s">
+        <v>1374</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>1185</v>
+      </c>
+      <c r="B73" t="s">
+        <v>1260</v>
+      </c>
+      <c r="D73" t="s">
+        <v>1358</v>
+      </c>
+      <c r="E73" t="s">
+        <v>40</v>
+      </c>
+      <c r="F73" t="s">
+        <v>1374</v>
+      </c>
+      <c r="I73" t="s">
+        <v>1415</v>
+      </c>
+      <c r="J73" t="s">
+        <v>55</v>
+      </c>
+      <c r="O73" t="s">
+        <v>1492</v>
+      </c>
+      <c r="P73" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>1186</v>
+      </c>
+      <c r="B74" t="s">
+        <v>1261</v>
+      </c>
+      <c r="E74" t="s">
+        <v>40</v>
+      </c>
+      <c r="F74" t="s">
+        <v>1375</v>
+      </c>
+      <c r="I74" t="s">
+        <v>1416</v>
+      </c>
+      <c r="J74" t="s">
+        <v>55</v>
+      </c>
+      <c r="O74" t="s">
+        <v>1453</v>
+      </c>
+      <c r="P74" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>1186</v>
+      </c>
+      <c r="B75" t="s">
+        <v>1262</v>
+      </c>
+      <c r="E75" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>1187</v>
+      </c>
+      <c r="B76" t="s">
+        <v>1263</v>
+      </c>
+      <c r="E76" t="s">
+        <v>40</v>
+      </c>
+      <c r="F76" t="s">
+        <v>1374</v>
+      </c>
+      <c r="I76" t="s">
+        <v>1417</v>
+      </c>
+      <c r="J76" t="s">
+        <v>55</v>
+      </c>
+      <c r="O76" t="s">
+        <v>1493</v>
+      </c>
+      <c r="P76" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>1188</v>
+      </c>
+      <c r="B77" t="s">
+        <v>1264</v>
+      </c>
+      <c r="D77" t="s">
+        <v>1359</v>
+      </c>
+      <c r="E77" t="s">
+        <v>40</v>
+      </c>
+      <c r="F77" t="s">
+        <v>1374</v>
+      </c>
+      <c r="I77" t="s">
+        <v>1418</v>
+      </c>
+      <c r="J77" t="s">
+        <v>55</v>
+      </c>
+      <c r="O77" t="s">
+        <v>1494</v>
+      </c>
+      <c r="P77" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>1189</v>
+      </c>
+      <c r="B78" t="s">
+        <v>1265</v>
+      </c>
+      <c r="E78" t="s">
+        <v>40</v>
+      </c>
+      <c r="F78" t="s">
+        <v>1374</v>
+      </c>
+      <c r="I78" t="s">
+        <v>1419</v>
+      </c>
+      <c r="J78" t="s">
+        <v>56</v>
+      </c>
+      <c r="O78" t="s">
+        <v>1495</v>
+      </c>
+      <c r="P78" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B79" t="s">
+        <v>1266</v>
+      </c>
+      <c r="D79" t="s">
+        <v>1360</v>
+      </c>
+      <c r="E79" t="s">
+        <v>40</v>
+      </c>
+      <c r="F79" t="s">
+        <v>1374</v>
+      </c>
+      <c r="I79" t="s">
+        <v>1420</v>
+      </c>
+      <c r="J79" t="s">
+        <v>55</v>
+      </c>
+      <c r="O79" t="s">
+        <v>1496</v>
+      </c>
+      <c r="P79" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B80" t="s">
+        <v>1267</v>
+      </c>
+      <c r="E80" t="s">
+        <v>40</v>
+      </c>
+      <c r="F80" t="s">
+        <v>1374</v>
+      </c>
+    </row>
+    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>1303</v>
+      </c>
+      <c r="B81" t="s">
+        <v>1268</v>
+      </c>
+      <c r="E81" t="s">
+        <v>40</v>
+      </c>
+      <c r="F81" t="s">
+        <v>1375</v>
+      </c>
+      <c r="I81" t="s">
+        <v>1421</v>
+      </c>
+      <c r="J81" t="s">
+        <v>55</v>
+      </c>
+      <c r="O81" t="s">
+        <v>1497</v>
+      </c>
+      <c r="P81" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>1304</v>
+      </c>
+      <c r="B82" t="s">
+        <v>1269</v>
+      </c>
+      <c r="E82" t="s">
+        <v>40</v>
+      </c>
+      <c r="F82" t="s">
+        <v>1374</v>
+      </c>
+      <c r="I82" t="s">
+        <v>1422</v>
+      </c>
+      <c r="J82" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>1305</v>
+      </c>
+      <c r="B83" t="s">
+        <v>1270</v>
+      </c>
+      <c r="E83" t="s">
+        <v>40</v>
+      </c>
+      <c r="F83" t="s">
+        <v>1374</v>
+      </c>
+      <c r="I83" t="s">
+        <v>1423</v>
+      </c>
+      <c r="J83" t="s">
+        <v>55</v>
+      </c>
+      <c r="O83" t="s">
+        <v>1498</v>
+      </c>
+      <c r="P83" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>1306</v>
+      </c>
+      <c r="B84" t="s">
+        <v>1271</v>
+      </c>
+      <c r="D84" t="s">
+        <v>1361</v>
+      </c>
+      <c r="E84" t="s">
+        <v>40</v>
+      </c>
+      <c r="F84" t="s">
+        <v>1374</v>
+      </c>
+      <c r="I84" t="s">
+        <v>1424</v>
+      </c>
+      <c r="J84" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>1307</v>
+      </c>
+      <c r="B85" t="s">
+        <v>1272</v>
+      </c>
+      <c r="D85" t="s">
+        <v>1362</v>
+      </c>
+      <c r="E85" t="s">
+        <v>40</v>
+      </c>
+      <c r="F85" t="s">
+        <v>1374</v>
+      </c>
+      <c r="I85">
+        <v>3136132416</v>
+      </c>
+      <c r="J85" t="s">
+        <v>55</v>
+      </c>
+      <c r="O85" t="s">
+        <v>1499</v>
+      </c>
+      <c r="P85" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B86" t="s">
+        <v>1273</v>
+      </c>
+      <c r="E86" t="s">
+        <v>40</v>
+      </c>
+      <c r="F86" t="s">
+        <v>1374</v>
+      </c>
+      <c r="I86">
+        <v>3127925075</v>
+      </c>
+      <c r="J86" t="s">
+        <v>55</v>
+      </c>
+      <c r="O86" t="s">
+        <v>1500</v>
+      </c>
+      <c r="P86" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>1309</v>
+      </c>
+      <c r="B87" t="s">
+        <v>1274</v>
+      </c>
+      <c r="E87" t="s">
+        <v>40</v>
+      </c>
+      <c r="F87" t="s">
+        <v>1374</v>
+      </c>
+      <c r="O87" t="s">
+        <v>1501</v>
+      </c>
+      <c r="P87" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>1310</v>
+      </c>
+      <c r="B88" t="s">
+        <v>1275</v>
+      </c>
+      <c r="D88" t="s">
+        <v>1363</v>
+      </c>
+      <c r="E88" t="s">
+        <v>40</v>
+      </c>
+      <c r="F88" t="s">
+        <v>1374</v>
+      </c>
+    </row>
+    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>1311</v>
+      </c>
+      <c r="B89" t="s">
+        <v>1276</v>
+      </c>
+      <c r="D89" t="s">
+        <v>1364</v>
+      </c>
+      <c r="E89" t="s">
+        <v>40</v>
+      </c>
+      <c r="F89" t="s">
+        <v>1374</v>
+      </c>
+      <c r="I89">
+        <v>3122701680</v>
+      </c>
+      <c r="J89" t="s">
+        <v>55</v>
+      </c>
+      <c r="O89" t="s">
+        <v>1502</v>
+      </c>
+      <c r="P89" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="90" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>1309</v>
+      </c>
+      <c r="B90" t="s">
+        <v>1277</v>
+      </c>
+      <c r="E90" t="s">
+        <v>40</v>
+      </c>
+      <c r="F90" t="s">
+        <v>1374</v>
+      </c>
+      <c r="I90" t="s">
+        <v>1425</v>
+      </c>
+      <c r="J90" t="s">
+        <v>56</v>
+      </c>
+      <c r="O90" t="s">
+        <v>1503</v>
+      </c>
+      <c r="P90" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="91" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>1309</v>
+      </c>
+      <c r="B91" t="s">
+        <v>1278</v>
+      </c>
+      <c r="D91" t="s">
+        <v>1365</v>
+      </c>
+      <c r="E91" t="s">
+        <v>40</v>
+      </c>
+      <c r="F91" t="s">
+        <v>1374</v>
+      </c>
+    </row>
+    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>1312</v>
+      </c>
+      <c r="B92" t="s">
+        <v>1279</v>
+      </c>
+      <c r="D92" t="s">
+        <v>1366</v>
+      </c>
+      <c r="E92" t="s">
+        <v>40</v>
+      </c>
+      <c r="F92" t="s">
+        <v>1374</v>
+      </c>
+      <c r="I92" t="s">
+        <v>1426</v>
+      </c>
+      <c r="J92" t="s">
+        <v>55</v>
+      </c>
+      <c r="O92" t="s">
+        <v>1504</v>
+      </c>
+      <c r="P92" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>1313</v>
+      </c>
+      <c r="B93" t="s">
+        <v>1280</v>
+      </c>
+      <c r="E93" t="s">
+        <v>40</v>
+      </c>
+      <c r="F93" t="s">
+        <v>1374</v>
+      </c>
+      <c r="O93" t="s">
+        <v>1505</v>
+      </c>
+      <c r="P93" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>1314</v>
+      </c>
+      <c r="B94" t="s">
+        <v>1281</v>
+      </c>
+      <c r="D94" t="s">
+        <v>1367</v>
+      </c>
+      <c r="E94" t="s">
+        <v>40</v>
+      </c>
+      <c r="F94" t="s">
+        <v>1374</v>
+      </c>
+      <c r="I94">
+        <v>3127598392</v>
+      </c>
+      <c r="J94" t="s">
+        <v>55</v>
+      </c>
+      <c r="O94" t="s">
+        <v>1506</v>
+      </c>
+      <c r="P94" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="95" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>1315</v>
+      </c>
+      <c r="B95" t="s">
+        <v>1282</v>
+      </c>
+      <c r="D95" t="s">
+        <v>1368</v>
+      </c>
+      <c r="E95" t="s">
+        <v>40</v>
+      </c>
+      <c r="F95" t="s">
+        <v>1375</v>
+      </c>
+    </row>
+    <row r="96" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>1316</v>
+      </c>
+      <c r="B96" t="s">
+        <v>1283</v>
+      </c>
+      <c r="E96" t="s">
+        <v>40</v>
+      </c>
+      <c r="F96" t="s">
+        <v>1375</v>
+      </c>
+    </row>
+    <row r="97" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>1317</v>
+      </c>
+      <c r="B97" t="s">
+        <v>1284</v>
+      </c>
+      <c r="E97" t="s">
+        <v>40</v>
+      </c>
+      <c r="F97" t="s">
+        <v>1374</v>
+      </c>
+      <c r="I97" t="s">
+        <v>1427</v>
+      </c>
+      <c r="J97" t="s">
+        <v>56</v>
+      </c>
+      <c r="O97" t="s">
+        <v>1507</v>
+      </c>
+      <c r="P97" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="98" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B98" t="s">
+        <v>1285</v>
+      </c>
+      <c r="D98" t="s">
+        <v>1369</v>
+      </c>
+      <c r="E98" t="s">
+        <v>40</v>
+      </c>
+      <c r="F98" t="s">
+        <v>1374</v>
+      </c>
+      <c r="I98" t="s">
+        <v>1428</v>
+      </c>
+      <c r="J98" t="s">
+        <v>55</v>
+      </c>
+      <c r="O98" t="s">
+        <v>1508</v>
+      </c>
+      <c r="P98" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="99" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>1319</v>
+      </c>
+      <c r="B99" t="s">
+        <v>1286</v>
+      </c>
+      <c r="D99" t="s">
+        <v>1370</v>
+      </c>
+      <c r="E99" t="s">
+        <v>40</v>
+      </c>
+      <c r="F99" t="s">
+        <v>1374</v>
+      </c>
+      <c r="I99" t="s">
+        <v>1429</v>
+      </c>
+      <c r="J99" t="s">
+        <v>55</v>
+      </c>
+      <c r="O99" t="s">
+        <v>1509</v>
+      </c>
+      <c r="P99" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="100" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>1320</v>
+      </c>
+      <c r="B100" t="s">
+        <v>807</v>
+      </c>
+      <c r="E100" t="s">
+        <v>40</v>
+      </c>
+      <c r="F100" t="s">
+        <v>1374</v>
+      </c>
+      <c r="I100" t="s">
+        <v>1430</v>
+      </c>
+      <c r="J100" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="101" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>1321</v>
+      </c>
+      <c r="B101" t="s">
+        <v>1287</v>
+      </c>
+      <c r="E101" t="s">
+        <v>40</v>
+      </c>
+      <c r="I101" t="s">
+        <v>1431</v>
+      </c>
+      <c r="J101" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="102" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>1322</v>
+      </c>
+      <c r="B102" t="s">
+        <v>1202</v>
+      </c>
+      <c r="E102" t="s">
+        <v>40</v>
+      </c>
+      <c r="F102" t="s">
+        <v>1374</v>
+      </c>
+    </row>
+    <row r="103" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>1323</v>
+      </c>
+      <c r="B103" t="s">
+        <v>1288</v>
+      </c>
+      <c r="E103" t="s">
+        <v>40</v>
+      </c>
+      <c r="F103" t="s">
+        <v>1374</v>
+      </c>
+      <c r="I103" t="s">
+        <v>1432</v>
+      </c>
+      <c r="J103" t="s">
+        <v>55</v>
+      </c>
+      <c r="O103" t="s">
+        <v>1510</v>
+      </c>
+      <c r="P103" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="104" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>1324</v>
+      </c>
+      <c r="B104" t="s">
+        <v>1289</v>
+      </c>
+      <c r="E104" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="105" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>1325</v>
+      </c>
+      <c r="B105" t="s">
+        <v>1290</v>
+      </c>
+      <c r="E105" t="s">
+        <v>40</v>
+      </c>
+      <c r="F105" t="s">
+        <v>1374</v>
+      </c>
+      <c r="I105" t="s">
+        <v>1433</v>
+      </c>
+      <c r="J105" t="s">
+        <v>55</v>
+      </c>
+      <c r="O105" t="s">
+        <v>1511</v>
+      </c>
+      <c r="P105" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="106" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>1326</v>
+      </c>
+      <c r="B106" t="s">
+        <v>1290</v>
+      </c>
+      <c r="E106" t="s">
+        <v>40</v>
+      </c>
+      <c r="F106" t="s">
+        <v>1374</v>
+      </c>
+      <c r="I106" t="s">
+        <v>1433</v>
+      </c>
+      <c r="J106" t="s">
+        <v>55</v>
+      </c>
+      <c r="O106" t="s">
+        <v>1511</v>
+      </c>
+      <c r="P106" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="107" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>1327</v>
+      </c>
+      <c r="B107" t="s">
+        <v>1291</v>
+      </c>
+      <c r="E107" t="s">
+        <v>40</v>
+      </c>
+      <c r="F107" t="s">
+        <v>1374</v>
+      </c>
+    </row>
+    <row r="108" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>1328</v>
+      </c>
+      <c r="B108" t="s">
+        <v>1292</v>
+      </c>
+      <c r="E108" t="s">
+        <v>40</v>
+      </c>
+      <c r="F108" t="s">
+        <v>1374</v>
+      </c>
+      <c r="I108" t="s">
+        <v>1434</v>
+      </c>
+      <c r="J108" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="109" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>1329</v>
+      </c>
+      <c r="B109" t="s">
+        <v>1293</v>
+      </c>
+      <c r="E109" t="s">
+        <v>40</v>
+      </c>
+      <c r="F109" t="s">
+        <v>1374</v>
+      </c>
+      <c r="I109" t="s">
+        <v>1435</v>
+      </c>
+      <c r="J109" t="s">
+        <v>56</v>
+      </c>
+      <c r="O109" t="s">
+        <v>1512</v>
+      </c>
+      <c r="P109" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="110" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>1330</v>
+      </c>
+      <c r="B110" t="s">
+        <v>1294</v>
+      </c>
+      <c r="E110" t="s">
+        <v>40</v>
+      </c>
+      <c r="F110" t="s">
+        <v>1374</v>
+      </c>
+    </row>
+    <row r="111" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>1331</v>
+      </c>
+      <c r="B111" t="s">
+        <v>811</v>
+      </c>
+      <c r="E111" t="s">
+        <v>40</v>
+      </c>
+      <c r="F111" t="s">
+        <v>1374</v>
+      </c>
+      <c r="I111">
+        <v>3103884757</v>
+      </c>
+      <c r="J111" t="s">
+        <v>56</v>
+      </c>
+      <c r="O111" t="s">
+        <v>1513</v>
+      </c>
+      <c r="P111" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="112" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>443</v>
+      </c>
+      <c r="B112" t="s">
+        <v>1295</v>
+      </c>
+      <c r="E112" t="s">
+        <v>40</v>
+      </c>
+      <c r="F112" t="s">
+        <v>1376</v>
+      </c>
+      <c r="I112">
+        <v>3192607089</v>
+      </c>
+      <c r="J112" t="s">
+        <v>56</v>
+      </c>
+      <c r="O112" t="s">
+        <v>1514</v>
+      </c>
+      <c r="P112" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="113" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>1332</v>
+      </c>
+      <c r="B113" t="s">
+        <v>1296</v>
+      </c>
+      <c r="D113" t="s">
+        <v>1371</v>
+      </c>
+      <c r="E113" t="s">
+        <v>40</v>
+      </c>
+      <c r="F113" t="s">
+        <v>1375</v>
+      </c>
+      <c r="I113">
+        <v>3137449764</v>
+      </c>
+      <c r="J113" t="s">
+        <v>56</v>
+      </c>
+      <c r="O113" t="s">
+        <v>1515</v>
+      </c>
+      <c r="P113" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="114" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>1333</v>
+      </c>
+      <c r="B114" t="s">
+        <v>1297</v>
+      </c>
+      <c r="D114" t="s">
+        <v>1372</v>
+      </c>
+      <c r="E114" t="s">
+        <v>40</v>
+      </c>
+      <c r="F114" t="s">
+        <v>1374</v>
+      </c>
+      <c r="I114" t="s">
+        <v>1436</v>
+      </c>
+      <c r="J114" t="s">
+        <v>55</v>
+      </c>
+      <c r="O114" t="s">
+        <v>1516</v>
+      </c>
+      <c r="P114" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="115" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>1334</v>
+      </c>
+      <c r="B115" t="s">
+        <v>1298</v>
+      </c>
+      <c r="E115" t="s">
+        <v>40</v>
+      </c>
+      <c r="F115" t="s">
+        <v>1374</v>
+      </c>
+      <c r="I115" t="s">
+        <v>1437</v>
+      </c>
+      <c r="J115" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="116" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>1335</v>
+      </c>
+      <c r="B116" t="s">
+        <v>1299</v>
+      </c>
+      <c r="E116" t="s">
+        <v>40</v>
+      </c>
+      <c r="F116" t="s">
+        <v>1374</v>
+      </c>
+      <c r="I116" t="s">
+        <v>1438</v>
+      </c>
+      <c r="J116" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="117" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>1336</v>
+      </c>
+      <c r="B117" t="s">
+        <v>1213</v>
+      </c>
+      <c r="E117" t="s">
+        <v>40</v>
+      </c>
+      <c r="F117" t="s">
+        <v>1374</v>
+      </c>
+      <c r="I117" t="s">
+        <v>1439</v>
+      </c>
+      <c r="J117" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="118" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>1337</v>
+      </c>
+      <c r="B118" t="s">
+        <v>1300</v>
+      </c>
+      <c r="D118" t="s">
+        <v>1373</v>
+      </c>
+      <c r="E118" t="s">
+        <v>40</v>
+      </c>
+      <c r="F118" t="s">
+        <v>1374</v>
+      </c>
+      <c r="I118" t="s">
+        <v>1440</v>
+      </c>
+      <c r="J118" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="119" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>1338</v>
+      </c>
+      <c r="B119" t="s">
+        <v>1301</v>
+      </c>
+      <c r="E119" t="s">
+        <v>40</v>
+      </c>
+      <c r="F119" t="s">
+        <v>1374</v>
+      </c>
+      <c r="I119" t="s">
+        <v>1441</v>
+      </c>
+      <c r="J119" t="s">
+        <v>55</v>
+      </c>
+      <c r="O119" t="s">
+        <v>1517</v>
+      </c>
+      <c r="P119" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="120" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>1339</v>
+      </c>
+      <c r="B120" t="s">
+        <v>1302</v>
+      </c>
+      <c r="E120" t="s">
+        <v>40</v>
+      </c>
+      <c r="F120" t="s">
+        <v>1374</v>
+      </c>
+      <c r="I120" t="s">
+        <v>1442</v>
+      </c>
+      <c r="J120" t="s">
+        <v>55</v>
+      </c>
+      <c r="O120" t="s">
+        <v>1518</v>
+      </c>
+      <c r="P120" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -4000,7 +7909,7 @@
           <x14:formula1>
             <xm:f>dropdown_list!$D$1:$D$3</xm:f>
           </x14:formula1>
-          <xm:sqref>J2:J50</xm:sqref>
+          <xm:sqref>J2:J50 J58</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Tipo de teléfono principal" prompt="Seleccionar de la lista despegable tipo de teléfono principal del cliente, si no hay teléfono principal dejar campo vacio." xr:uid="{00000000-0002-0000-0000-00000B000000}">
           <x14:formula1>
@@ -4077,7 +7986,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AW125"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -7941,6 +11850,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="85ea12e4-2a02-4a9e-9704-cf32ec2a8bb7" xsi:nil="true"/>
@@ -7949,15 +11867,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8196,20 +12105,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C494E5C2-A1A6-4785-9E09-C7B94C17F21B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0DB67196-8AC9-457A-9D19-FB6DA8581EFA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="85ea12e4-2a02-4a9e-9704-cf32ec2a8bb7"/>
     <ds:schemaRef ds:uri="10005bed-8d80-4780-a97d-5ee5e6679709"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C494E5C2-A1A6-4785-9E09-C7B94C17F21B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
